--- a/shriram-page-metadata.xlsx
+++ b/shriram-page-metadata.xlsx
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Loan Against Stocks (LAS) | Shriram Financial Services</t>
+          <t>Loan Against Shares (LAS) | Shriram Financial Services</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Get up to 4x buying power with Margin Trading Facility (MTF) from Shriram Financial Services - no overnight square-off, 500+ eligible stocks.</t>
+          <t>Get up to 4x buying power with Margin Trading Facility (MTF) from Shriram Financial Services - no overnight square-off, 700+ eligible stocks.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
